--- a/data/bencmark_rjesenja.xlsx
+++ b/data/bencmark_rjesenja.xlsx
@@ -416,9 +416,1030 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>GA1</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>VRPBGA1</t>
+        </is>
+      </c>
+      <c r="C1" t="n">
+        <v>230722.15</v>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>229885.65</t>
+        </is>
+      </c>
+      <c r="E1" t="n">
+        <v>836.5000000000291</v>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="G1" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1" t="n">
+        <v>25</v>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K1" t="n">
+        <v>1579</v>
+      </c>
+      <c r="L1" t="n">
+        <v>10049</v>
+      </c>
+      <c r="M1" t="n">
+        <v>2540</v>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>1550</t>
+        </is>
+      </c>
+      <c r="O1" t="n">
+        <v>1053.24</v>
+      </c>
+      <c r="P1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1" t="n">
+        <v>1053.24</v>
+      </c>
+      <c r="R1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GA1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VRPBGA1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>230722.15</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>229885.65</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>836.5000000000291</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1579</v>
+      </c>
+      <c r="L2" t="n">
+        <v>10049</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2540</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1550</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>1053.24</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1053.24</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GA2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>VRPBGA2</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>181279.41</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>180119.21</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1160.199999999983</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>25</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>3616</v>
+      </c>
+      <c r="L3" t="n">
+        <v>10049</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2540</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2550</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>1053.24</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1053.24</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GA3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VRPBGA3</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>163641.64</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>163405.38</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>236.2599999999802</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>5475</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10049</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2540</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4050</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>1053.25</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1053.25</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GB1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VRPBGB1</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>248187.78</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>239080.15</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>9107.629999999976</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>4769</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9840</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5228</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>1260.66</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1260.66</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GB2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VRPBGB2</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>201711.03</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>198047.77</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3663.260000000038</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>11181</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9840</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5228</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>1260.67</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1260.67</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GB3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VRPBGB3</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>170541.38</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>169372.29</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1169.089999999997</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>30</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>21000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9840</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5228</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>1260.66</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1260.66</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GC1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VRPBGC1</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>262787.86</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>250556.77</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>12231.09</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>40</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>7850</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9993</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10306</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>1698.26</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1698.26</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GC2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VRPBGC2</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>230369.52</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>215020.23</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>15349.29000000001</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>40</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>15920</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9993</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10306</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>1698.25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1698.25</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GC3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VRPBGC3</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>202294.49</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>199345.96</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2948.530000000028</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>40</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>41623</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9993</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10306</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4150</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>1698.26</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1698.26</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GD1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VRPBGD1</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>324149.86</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>322530.13</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1619.729999999981</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>38</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>3989</v>
+      </c>
+      <c r="L11" t="n">
+        <v>16297</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4208</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>1715.07</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1715.07</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GD2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VRPBGD2</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>323408.13</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>316708.86</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6699.270000000019</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>11</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>38</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>3989</v>
+      </c>
+      <c r="L12" t="n">
+        <v>16297</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4208</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>1715.07</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1715.07</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GD3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VRPBGD3</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>243407.64</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>239478.63</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3929.010000000009</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>38</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>10983</v>
+      </c>
+      <c r="L13" t="n">
+        <v>16297</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4208</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>1715.08</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1715.08</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GE1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VRPBGE1</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>244538.5</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>238879.58</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5658.920000000013</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>45</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>28465</v>
+      </c>
+      <c r="L14" t="n">
+        <v>15654</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7040</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2650</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>1898.66</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1898.66</v>
+      </c>
+      <c r="R14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GE2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VRPBGE2</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>214118.63</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>212263.11</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1855.520000000019</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>45</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>82656</v>
+      </c>
+      <c r="L15" t="n">
+        <v>15654</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7040</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4300</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>1898.67</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1898.67</v>
+      </c>
+      <c r="R15" t="n">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/bencmark_rjesenja.xlsx
+++ b/data/bencmark_rjesenja.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1437,6 +1437,686 @@
       </c>
       <c r="R15" t="n">
         <v>17</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GE1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VRPBGE1</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>244538.5</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>238879.58</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5658.920000000013</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>45</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>28465</v>
+      </c>
+      <c r="L16" t="n">
+        <v>15654</v>
+      </c>
+      <c r="M16" t="n">
+        <v>7040</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2650</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>1898.66</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1898.66</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GE2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VRPBGE2</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>214118.63</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>212263.11</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1855.520000000019</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>45</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>82656</v>
+      </c>
+      <c r="L17" t="n">
+        <v>15654</v>
+      </c>
+      <c r="M17" t="n">
+        <v>7040</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>4300</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>1898.67</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1898.67</v>
+      </c>
+      <c r="R17" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GE3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>VRPBGE3</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>211422.58</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>206659.17</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4763.409999999974</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>45</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>126136</v>
+      </c>
+      <c r="L18" t="n">
+        <v>15654</v>
+      </c>
+      <c r="M18" t="n">
+        <v>7040</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>1898.67</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1898.67</v>
+      </c>
+      <c r="R18" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GF1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>VRPBGF1</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>277377.92</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>263173.96</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>14203.96000000002</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>76868</v>
+      </c>
+      <c r="L19" t="n">
+        <v>14498</v>
+      </c>
+      <c r="M19" t="n">
+        <v>16410</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>2585.67</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2585.67</v>
+      </c>
+      <c r="R19" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GF2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>VRPBGF2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>277377.92</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>265214.16</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>12163.76000000007</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4.59</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>76868</v>
+      </c>
+      <c r="L20" t="n">
+        <v>14498</v>
+      </c>
+      <c r="M20" t="n">
+        <v>16410</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>2585.67</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2585.67</v>
+      </c>
+      <c r="R20" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GF3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>VRPBGF3</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>244889.79</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>241120.77</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3769.01999999999</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>60</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>183224</v>
+      </c>
+      <c r="L21" t="n">
+        <v>14498</v>
+      </c>
+      <c r="M21" t="n">
+        <v>16410</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>4400</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>2585.66</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2585.66</v>
+      </c>
+      <c r="R21" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GG1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>VRPBGG1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>339130.5</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>306305.4</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>32825.09999999998</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>10.72</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>57</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>22925</v>
+      </c>
+      <c r="L22" t="n">
+        <v>23833</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5603</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>2462.5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2462.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GG2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>VRPBGG2</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>253446.01</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>245440.99</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>8005.020000000019</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>57</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>50087</v>
+      </c>
+      <c r="L23" t="n">
+        <v>23833</v>
+      </c>
+      <c r="M23" t="n">
+        <v>5603</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>4300</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>2462.5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2462.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GG3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VRPBGG3</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>250677.84</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>229507.48</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>21170.36000000002</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>9.22</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>57</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>74748</v>
+      </c>
+      <c r="L24" t="n">
+        <v>23833</v>
+      </c>
+      <c r="M24" t="n">
+        <v>5603</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>2462.5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2462.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GH1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>VRPBGH1</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>277184.38</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>268933.06</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>8251.320000000007</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>6</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>68</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>185259</v>
+      </c>
+      <c r="L25" t="n">
+        <v>21201</v>
+      </c>
+      <c r="M25" t="n">
+        <v>11481</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>2734.83</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2734.83</v>
+      </c>
+      <c r="R25" t="n">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
